--- a/artfynd/A 32319-2025 artfynd.xlsx
+++ b/artfynd/A 32319-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126740261</v>
       </c>
       <c r="B2" t="n">
-        <v>96989</v>
+        <v>97064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32319-2025 artfynd.xlsx
+++ b/artfynd/A 32319-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126740261</v>
       </c>
       <c r="B2" t="n">
-        <v>97064</v>
+        <v>97070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32319-2025 artfynd.xlsx
+++ b/artfynd/A 32319-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126740261</v>
       </c>
       <c r="B2" t="n">
-        <v>97070</v>
+        <v>97071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32319-2025 artfynd.xlsx
+++ b/artfynd/A 32319-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126740261</v>
       </c>
       <c r="B2" t="n">
-        <v>97071</v>
+        <v>97075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32319-2025 artfynd.xlsx
+++ b/artfynd/A 32319-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,125 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127685269</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56853</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Götsered, Sandhult, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>371526</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6403377</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sandhult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Johansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32319-2025 artfynd.xlsx
+++ b/artfynd/A 32319-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127685269</v>
       </c>
       <c r="B3" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32319-2025 artfynd.xlsx
+++ b/artfynd/A 32319-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127685269</v>
       </c>
       <c r="B3" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32319-2025 artfynd.xlsx
+++ b/artfynd/A 32319-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127685269</v>
       </c>
       <c r="B3" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32319-2025 artfynd.xlsx
+++ b/artfynd/A 32319-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126740261</v>
       </c>
       <c r="B2" t="n">
-        <v>97075</v>
+        <v>97064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32319-2025 artfynd.xlsx
+++ b/artfynd/A 32319-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127685269</v>
       </c>
       <c r="B3" t="n">
-        <v>56864</v>
+        <v>57044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32319-2025 artfynd.xlsx
+++ b/artfynd/A 32319-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127685269</v>
       </c>
       <c r="B3" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32319-2025 artfynd.xlsx
+++ b/artfynd/A 32319-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127685269</v>
       </c>
       <c r="B3" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
